--- a/uploads/new.xlsx
+++ b/uploads/new.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahil\OneDrive\Desktop\software\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D074540-2B62-4B4D-A69A-7D72AD3DE6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269D1780-8631-4326-9A75-DF8A99A71AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="room1" sheetId="1" r:id="rId1"/>
     <sheet name="room2" sheetId="2" r:id="rId2"/>
     <sheet name="room3" sheetId="3" r:id="rId3"/>
     <sheet name="room4" sheetId="4" r:id="rId4"/>
-    <sheet name="room5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="22">
   <si>
     <t>Day</t>
   </si>
@@ -92,6 +91,9 @@
   </si>
   <si>
     <t>Friday</t>
+  </si>
+  <si>
+    <t>time</t>
   </si>
 </sst>
 </file>
@@ -127,8 +129,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -443,146 +446,175 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -593,7 +625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D171BD-FBE4-4174-AED2-C0C396D8646C}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -627,146 +659,175 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -777,7 +838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47EDFA02-7FF7-469E-9BCD-CF5D73D80AD6}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -811,109 +872,109 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
@@ -922,35 +983,64 @@
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
         <v>14</v>
       </c>
     </row>
@@ -961,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4C7D75-96B3-406A-AFDF-44C30E972F92}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -995,330 +1085,175 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CAD163-EB13-41A5-9DF8-FBCF2C8E0C59}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
         <v>16</v>
       </c>
     </row>
